--- a/docs/Evidence/Evidence_Matrix_Koromacno_07-10-2026.xlsx
+++ b/docs/Evidence/Evidence_Matrix_Koromacno_07-10-2026.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Evidence_Matrix_Koromacno_25-09" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="evidence" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
   <si>
     <t xml:space="preserve">Dokument</t>
   </si>
@@ -214,13 +214,13 @@
     <t xml:space="preserve">U PROCEDURI</t>
   </si>
   <si>
-    <t xml:space="preserve">Dokument: DOKAZ 3 (ZPPI-02)</t>
+    <t xml:space="preserve">Dokument: DOKAZ 3 (ZPPI-02 stara verzija)</t>
   </si>
   <si>
     <t xml:space="preserve">Grad Labin</t>
   </si>
   <si>
-    <t xml:space="preserve">Zahtjev za pristup informacijama - ugovorni odnosi, tehnička dokumentacija i evidencija izmjena sustava transparentnosti proračuna za konta 3233 i 3237</t>
+    <t xml:space="preserve">Zahtjev za pristup informacijama - ugovorni odnosi, tehnička dokumentacija i evidencija izmjena sustava transparentnosti proračuna za konta 3233 i 3237.</t>
   </si>
   <si>
     <t xml:space="preserve">ZPPI-04 - Zahtjev za pristup informacijama (prekogranični otpad)</t>
@@ -251,6 +251,60 @@
   </si>
   <si>
     <t xml:space="preserve">docs/ZPPI-05/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FZOEU odluka o sanaciji PPK Velebit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03.10.2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FZOEU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podjela na 4 faze: folija 20.000 m² (270.000 EUR), Faza 1: 4.500 t opasnog otpada (8,8 mil. EUR, CE-ZA-R/CIAK/Saubermacher), Faza 2: 650 t Holcim/Nexe (357.500 EUR), Faza 3: 32.915 t zakopanog otpada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FZOEU, službena stranica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CINEA Grant Agreement ID: 101133120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europska komisija / CINEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grant Agreement za KOdeCO Net Zero, 116.926.000 EUR. Vezanost sredstava uz valjanost SUO postupka u Hrvatskoj.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CINEA registar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US v. Vuk Vukovic, Sealed Complaint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US District Court, Southern District of New York</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Postojanje kaznenog postupka zbog securities fraud i wire fraud. Nije dokaz veze s Koromačnom bez dodatnih dokaza.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.justice.gov/usao-sdny/media/1461011/dl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOKAZANO postojanje postupka; nije dokaz veze s Koromačnom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZPPI Grad Labin (novi zahtjev)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07.10.2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahtjev za pristup informacijama o nabavi, ugovorima, IT sustavima (CityX, Libusoft) i integritetu podataka proračunskog portala. Rok 22.10.2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/ZPPI-02/ZAHTJEV_ZA_PRISTUP_INFORMACIJAMA_GRAD_LABIN.pdf</t>
   </si>
 </sst>
 </file>
@@ -452,16 +506,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="53.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="49.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="47.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="124.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="38.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="171.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="64.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="54.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -774,6 +828,98 @@
         <v>76</v>
       </c>
       <c r="G14" s="0" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>101133120</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="0" t="s">
         <v>73</v>
       </c>
     </row>
